--- a/docs/FAQ跳转映射表.xlsx
+++ b/docs/FAQ跳转映射表.xlsx
@@ -15,7 +15,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'分类直达'!$A$1:$D$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'问题直达'!$A$1:$G$61</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'问题直达'!$A$1:$G$59</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'功能页面跳转'!$A$1:$E$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'页脚按钮'!$A$1:$C$5</definedName>
   </definedNames>
@@ -499,7 +499,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026.10</t>
+          <t>2026.10.29</t>
         </is>
       </c>
     </row>
@@ -511,7 +511,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>js/faq-data.zh.js（10 个分类 / 60 条问题）</t>
+          <t>js/faq-data.zh.js（10 个分类 / 58 条问题；原页面答案为空的 q-about-05、q-order-01 已删除）</t>
         </is>
       </c>
     </row>
@@ -547,19 +547,19 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>需要确认或补充的项目（备注 / 状态列有说明）</t>
+          <t>仍需确认的项目（状态列有说明）</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>填写方法</t>
+          <t>URL 来源</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>功能页面 URL 确认后，填入「功能页面跳转」表的 C 列，并同步写入 faq-data.zh.js 的 FAQ_LINKS</t>
+          <t>主站 www.global-png.com 前端路由表（2026-10-29 读取）；修改时同步更新 faq-data.zh.js 的 FAQ_LINKS 和 index.html 页脚</t>
         </is>
       </c>
     </row>
@@ -617,7 +617,7 @@
         </is>
       </c>
       <c r="C2" s="5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
@@ -817,7 +817,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G61"/>
+  <dimension ref="A1:G59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -867,325 +867,293 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="5" t="inlineStr">
         <is>
           <t>关于平台</t>
         </is>
       </c>
-      <c r="B2" s="6" t="inlineStr">
+      <c r="B2" s="5" t="inlineStr">
         <is>
           <t>q-about-01</t>
         </is>
       </c>
-      <c r="C2" s="6" t="inlineStr">
-        <is>
-          <t>Global-PNG 是什么？能为采购方解决哪些问题？</t>
-        </is>
-      </c>
-      <c r="D2" s="6" t="inlineStr">
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Global-PNG 是什么？能为采购方解决什么问题？</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
         <is>
           <t>#q-about-01</t>
         </is>
       </c>
-      <c r="E2" s="6" t="inlineStr">
+      <c r="E2" s="5" t="inlineStr">
         <is>
           <t>https://www.global-png.com/act/pngFAQ.html#q-about-01</t>
         </is>
       </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G2" s="6" t="inlineStr">
-        <is>
-          <t>韩文机翻回译的中文，需与原页面原文核对</t>
-        </is>
-      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G2" s="5" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>关于平台</t>
         </is>
       </c>
-      <c r="B3" s="6" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>q-about-02</t>
         </is>
       </c>
-      <c r="C3" s="6" t="inlineStr">
-        <is>
-          <t>普恩志与阿里巴巴国际站、中国制造网等综合 B2B 平台有什么区别？</t>
-        </is>
-      </c>
-      <c r="D3" s="6" t="inlineStr">
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>普恩志和阿里巴巴国际站、Made-in-China 等综合 B2B 平台有什么不同？</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
         <is>
           <t>#q-about-02</t>
         </is>
       </c>
-      <c r="E3" s="6" t="inlineStr">
+      <c r="E3" s="5" t="inlineStr">
         <is>
           <t>https://www.global-png.com/act/pngFAQ.html#q-about-02</t>
         </is>
       </c>
-      <c r="F3" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G3" s="6" t="inlineStr">
-        <is>
-          <t>韩文机翻回译的中文，需与原页面原文核对</t>
-        </is>
-      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>关于平台</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>q-about-03</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>平台的两个域名有什么区别？</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
+      <c r="D4" s="5" t="inlineStr">
         <is>
           <t>#q-about-03</t>
         </is>
       </c>
-      <c r="E4" s="6" t="inlineStr">
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>https://www.global-png.com/act/pngFAQ.html#q-about-03</t>
         </is>
       </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G4" s="6" t="inlineStr">
-        <is>
-          <t>韩文机翻回译的中文，需与原页面原文核对</t>
-        </is>
-      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>关于平台</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>q-about-04</t>
         </is>
       </c>
-      <c r="C5" s="6" t="inlineStr">
-        <is>
-          <t>普恩志的公司背景、发展历程和规模如何？</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>普恩志的公司背景、发展历程、规模如何？</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>#q-about-04</t>
         </is>
       </c>
-      <c r="E5" s="6" t="inlineStr">
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>https://www.global-png.com/act/pngFAQ.html#q-about-04</t>
         </is>
       </c>
-      <c r="F5" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="6" t="inlineStr">
-        <is>
-          <t>韩文机翻回译的中文，需与原页面原文核对</t>
-        </is>
-      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>关于平台</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>q-about-05</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>普恩志的使命、愿景和目标是什么？</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>#q-about-05</t>
-        </is>
-      </c>
-      <c r="E6" s="6" t="inlineStr">
-        <is>
-          <t>https://www.global-png.com/act/pngFAQ.html#q-about-05</t>
-        </is>
-      </c>
-      <c r="F6" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G6" s="6" t="inlineStr">
-        <is>
-          <t>保存页面时答案内容丢失（只剩 "&gt; &gt; &gt;"），需从原页面补充</t>
-        </is>
-      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>q-about-06</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>平台的"四方协同"商业模式是什么？</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>#q-about-06</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>https://www.global-png.com/act/pngFAQ.html#q-about-06</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>关于平台</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>q-about-06</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>平台的“四方协同”商业模式是什么？</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>#q-about-06</t>
-        </is>
-      </c>
-      <c r="E7" s="6" t="inlineStr">
-        <is>
-          <t>https://www.global-png.com/act/pngFAQ.html#q-about-06</t>
-        </is>
-      </c>
-      <c r="F7" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G7" s="6" t="inlineStr">
-        <is>
-          <t>韩文机翻回译的中文，需与原页面原文核对</t>
-        </is>
-      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>q-about-07</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>平台有哪些生态支撑？</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>#q-about-07</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>https://www.global-png.com/act/pngFAQ.html#q-about-07</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>关于平台</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>q-about-07</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>支撑平台的生态体系是什么？</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>#q-about-07</t>
-        </is>
-      </c>
-      <c r="E8" s="6" t="inlineStr">
-        <is>
-          <t>https://www.global-png.com/act/pngFAQ.html#q-about-07</t>
-        </is>
-      </c>
-      <c r="F8" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="6" t="inlineStr">
-        <is>
-          <t>韩文机翻回译的中文，需与原页面原文核对</t>
-        </is>
-      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>q-about-08</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>平台可以提供哪些事业领域服务？</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>#q-about-08</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>https://www.global-png.com/act/pngFAQ.html#q-about-08</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="inlineStr">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>关于平台</t>
         </is>
       </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>q-about-08</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>平台可以为哪些事业领域提供服务？</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>#q-about-08</t>
-        </is>
-      </c>
-      <c r="E9" s="6" t="inlineStr">
-        <is>
-          <t>https://www.global-png.com/act/pngFAQ.html#q-about-08</t>
-        </is>
-      </c>
-      <c r="F9" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G9" s="6" t="inlineStr">
-        <is>
-          <t>韩文机翻回译的中文，需与原页面原文核对（仅问题）</t>
-        </is>
-      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>q-about-09</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>如何联系平台客服？有没有线下办公点？</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>#q-about-09</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>https://www.global-png.com/act/pngFAQ.html#q-about-09</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>关于平台</t>
+          <t>注册与账户</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>q-about-09</t>
+          <t>q-account-01</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>如何联系平台客服？有没有线下办公点？</t>
+          <t>如何注册账户？支持哪些方式？</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>#q-about-09</t>
+          <t>#q-account-01</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>https://www.global-png.com/act/pngFAQ.html#q-about-09</t>
+          <t>https://www.global-png.com/act/pngFAQ.html#q-account-01</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
@@ -1203,27 +1171,27 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>q-account-01</t>
+          <t>q-account-02</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>如何注册账户？支持哪些方式？</t>
+          <t>如何进行企业认证？</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>#q-account-01</t>
+          <t>#q-account-02</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>https://www.global-png.com/act/pngFAQ.html#q-account-01</t>
+          <t>https://www.global-png.com/act/pngFAQ.html#q-account-02</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>enterpriseAuth</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr"/>
@@ -1236,27 +1204,27 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>q-account-02</t>
+          <t>q-account-03</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>如何进行企业认证？</t>
+          <t>账户安全有哪些设置？</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>#q-account-02</t>
+          <t>#q-account-03</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>https://www.global-png.com/act/pngFAQ.html#q-account-02</t>
+          <t>https://www.global-png.com/act/pngFAQ.html#q-account-03</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>enterpriseAuth</t>
+          <t>accountSecurity</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr"/>
@@ -1269,27 +1237,27 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>q-account-03</t>
+          <t>q-account-04</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>账户安全有哪些设置？</t>
+          <t>企业子账号如何管理？</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>#q-account-03</t>
+          <t>#q-account-04</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>https://www.global-png.com/act/pngFAQ.html#q-account-03</t>
+          <t>https://www.global-png.com/act/pngFAQ.html#q-account-04</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>accountSecurity</t>
+          <t>subAccount</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr"/>
@@ -1302,27 +1270,27 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>q-account-04</t>
+          <t>q-account-05</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>企业子账号如何管理？</t>
+          <t>收货地址如何管理？</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>#q-account-04</t>
+          <t>#q-account-05</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>https://www.global-png.com/act/pngFAQ.html#q-account-04</t>
+          <t>https://www.global-png.com/act/pngFAQ.html#q-account-05</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>subAccount</t>
+          <t>addressManage</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr"/>
@@ -1330,32 +1298,32 @@
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>注册与账户</t>
+          <t>产品与搜索</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>q-account-05</t>
+          <t>q-product-01</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>收货地址如何管理？</t>
+          <t>平台上有哪些产品品类？</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>#q-account-05</t>
+          <t>#q-product-01</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>https://www.global-png.com/act/pngFAQ.html#q-account-05</t>
+          <t>https://www.global-png.com/act/pngFAQ.html#q-product-01</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>addressManage</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr"/>
@@ -1368,22 +1336,22 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>q-product-01</t>
+          <t>q-product-02</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>平台上有哪些产品品类？</t>
+          <t>平台覆盖哪些设备品类（CVD/刻蚀/检测等）？</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>#q-product-01</t>
+          <t>#q-product-02</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>https://www.global-png.com/act/pngFAQ.html#q-product-01</t>
+          <t>https://www.global-png.com/act/pngFAQ.html#q-product-02</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
@@ -1401,22 +1369,22 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>q-product-02</t>
+          <t>q-product-03</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>平台覆盖哪些设备品类（CVD/刻蚀/检测等）？</t>
+          <t>如何快速找到需要的设备？三种方式效率对比？</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>#q-product-02</t>
+          <t>#q-product-03</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>https://www.global-png.com/act/pngFAQ.html#q-product-02</t>
+          <t>https://www.global-png.com/act/pngFAQ.html#q-product-03</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
@@ -1427,41 +1395,37 @@
       <c r="G17" s="5" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="6" t="inlineStr">
+      <c r="A18" s="5" t="inlineStr">
         <is>
           <t>产品与搜索</t>
         </is>
       </c>
-      <c r="B18" s="6" t="inlineStr">
-        <is>
-          <t>q-product-03</t>
-        </is>
-      </c>
-      <c r="C18" s="6" t="inlineStr">
-        <is>
-          <t>如何快速找到需要的设备？三种方式效率对比？</t>
-        </is>
-      </c>
-      <c r="D18" s="6" t="inlineStr">
-        <is>
-          <t>#q-product-03</t>
-        </is>
-      </c>
-      <c r="E18" s="6" t="inlineStr">
-        <is>
-          <t>https://www.global-png.com/act/pngFAQ.html#q-product-03</t>
-        </is>
-      </c>
-      <c r="F18" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G18" s="6" t="inlineStr">
-        <is>
-          <t>表头部分列名缺失（空白列），需与原页面核对</t>
-        </is>
-      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>q-product-04</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>"国产替代"专区是什么？包含哪些品类？</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>#q-product-04</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>https://www.global-png.com/act/pngFAQ.html#q-product-04</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>domesticAlt</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
@@ -1471,22 +1435,22 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>q-product-04</t>
+          <t>q-product-05</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>"国产替代"专区是什么？包含哪些品类？</t>
+          <t>"海外优替"专区有什么？</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>#q-product-04</t>
+          <t>#q-product-05</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>https://www.global-png.com/act/pngFAQ.html#q-product-04</t>
+          <t>https://www.global-png.com/act/pngFAQ.html#q-product-05</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
@@ -1504,22 +1468,22 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>q-product-05</t>
+          <t>q-product-06</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>"海外优替"专区有什么？</t>
+          <t>产品详情页包含哪些信息？</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>#q-product-05</t>
+          <t>#q-product-06</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>https://www.global-png.com/act/pngFAQ.html#q-product-05</t>
+          <t>https://www.global-png.com/act/pngFAQ.html#q-product-06</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
@@ -1537,27 +1501,27 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>q-product-06</t>
+          <t>q-product-07</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>产品详情页包含哪些信息？</t>
+          <t>"物料编码"功能怎么用？</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>#q-product-06</t>
+          <t>#q-product-07</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>https://www.global-png.com/act/pngFAQ.html#q-product-06</t>
+          <t>https://www.global-png.com/act/pngFAQ.html#q-product-07</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>materialCode</t>
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr"/>
@@ -1565,72 +1529,68 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>产品与搜索</t>
+          <t>采购与订单</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>q-product-07</t>
+          <t>q-order-02</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>"物料编码"功能怎么用？</t>
+          <t>如何下单采购？有哪几种方式？</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>#q-product-07</t>
+          <t>#q-order-02</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>https://www.global-png.com/act/pngFAQ.html#q-product-07</t>
+          <t>https://www.global-png.com/act/pngFAQ.html#q-order-02</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>materialCode</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="6" t="inlineStr">
+      <c r="A23" s="5" t="inlineStr">
         <is>
           <t>采购与订单</t>
         </is>
       </c>
-      <c r="B23" s="6" t="inlineStr">
-        <is>
-          <t>q-order-01</t>
-        </is>
-      </c>
-      <c r="C23" s="6" t="inlineStr">
-        <is>
-          <t>订单的生命周期是怎样的？</t>
-        </is>
-      </c>
-      <c r="D23" s="6" t="inlineStr">
-        <is>
-          <t>#q-order-01</t>
-        </is>
-      </c>
-      <c r="E23" s="6" t="inlineStr">
-        <is>
-          <t>https://www.global-png.com/act/pngFAQ.html#q-order-01</t>
-        </is>
-      </c>
-      <c r="F23" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G23" s="6" t="inlineStr">
-        <is>
-          <t>原页面的订单状态流转图在保存时丢失，需补充状态流程</t>
-        </is>
-      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>q-order-03</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>"设计师申请单"是什么？</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>#q-order-03</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>https://www.global-png.com/act/pngFAQ.html#q-order-03</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
@@ -1640,27 +1600,27 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>q-order-02</t>
+          <t>q-order-04</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>如何下单采购？有哪几种方式？</t>
+          <t>常购清单有什么作用？</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>#q-order-02</t>
+          <t>#q-order-04</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>https://www.global-png.com/act/pngFAQ.html#q-order-02</t>
+          <t>https://www.global-png.com/act/pngFAQ.html#q-order-04</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>frequentList</t>
         </is>
       </c>
       <c r="G24" s="5" t="inlineStr"/>
@@ -1673,27 +1633,27 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>q-order-03</t>
+          <t>q-order-05</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>"设计师申请单"是什么？</t>
+          <t>投标和招标系统怎么用？</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>#q-order-03</t>
+          <t>#q-order-05</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>https://www.global-png.com/act/pngFAQ.html#q-order-03</t>
+          <t>https://www.global-png.com/act/pngFAQ.html#q-order-05</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>myTender</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr"/>
@@ -1706,27 +1666,27 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>q-order-04</t>
+          <t>q-order-06</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>常购清单有什么作用？</t>
+          <t>"我的项目"是什么功能？</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>#q-order-04</t>
+          <t>#q-order-06</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>https://www.global-png.com/act/pngFAQ.html#q-order-04</t>
+          <t>https://www.global-png.com/act/pngFAQ.html#q-order-06</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>myProject</t>
         </is>
       </c>
       <c r="G26" s="5" t="inlineStr"/>
@@ -1739,22 +1699,22 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>q-order-05</t>
+          <t>q-order-07</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>投标和招标系统怎么用？</t>
+          <t>采购流程大概需要多久？各环节时间分布</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>#q-order-05</t>
+          <t>#q-order-07</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>https://www.global-png.com/act/pngFAQ.html#q-order-05</t>
+          <t>https://www.global-png.com/act/pngFAQ.html#q-order-07</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
@@ -1772,22 +1732,22 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>q-order-06</t>
+          <t>q-order-08</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>"我的项目"是什么功能？</t>
+          <t>设备到货后怎么验收？三步验收法</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>#q-order-06</t>
+          <t>#q-order-08</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>https://www.global-png.com/act/pngFAQ.html#q-order-06</t>
+          <t>https://www.global-png.com/act/pngFAQ.html#q-order-08</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
@@ -1800,27 +1760,27 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>采购与订单</t>
+          <t>样品申请</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>q-order-07</t>
+          <t>q-sample-01</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>采购流程大概需要多久？各环节时间分布</t>
+          <t>平台的样品申请规则是什么？免费申样怎么申请？</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>#q-order-07</t>
+          <t>#q-sample-01</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>https://www.global-png.com/act/pngFAQ.html#q-order-07</t>
+          <t>https://www.global-png.com/act/pngFAQ.html#q-sample-01</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
@@ -1833,27 +1793,27 @@
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>采购与订单</t>
+          <t>跨境贸易（中韩双向专题）</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>q-order-08</t>
+          <t>q-cross-01</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>设备到货后怎么验收？三步验收法</t>
+          <t>韩国进口设备和国产设备怎么选？三个核心因素</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>#q-order-08</t>
+          <t>#q-cross-01</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>https://www.global-png.com/act/pngFAQ.html#q-order-08</t>
+          <t>https://www.global-png.com/act/pngFAQ.html#q-cross-01</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
@@ -1866,27 +1826,27 @@
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>样品申请</t>
+          <t>跨境贸易（中韩双向专题）</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>q-sample-01</t>
+          <t>q-cross-02</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>平台的样品申请规则是什么？免费申样怎么申请？</t>
+          <t>从韩国买二手半导体设备值不值得？哪些适合买？</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>#q-sample-01</t>
+          <t>#q-cross-02</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>https://www.global-png.com/act/pngFAQ.html#q-sample-01</t>
+          <t>https://www.global-png.com/act/pngFAQ.html#q-cross-02</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
@@ -1904,22 +1864,22 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>q-cross-01</t>
+          <t>q-cross-03</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>韩国进口设备和国产设备怎么选？三个核心因素</t>
+          <t>韩国二手设备市场的规模和特点？</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>#q-cross-01</t>
+          <t>#q-cross-03</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>https://www.global-png.com/act/pngFAQ.html#q-cross-01</t>
+          <t>https://www.global-png.com/act/pngFAQ.html#q-cross-03</t>
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr">
@@ -1937,22 +1897,22 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>q-cross-02</t>
+          <t>q-cross-04</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>从韩国买二手半导体设备值不值得？哪些适合买？</t>
+          <t>韩国设备进口需要什么手续和资质？5 步完整流程</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>#q-cross-02</t>
+          <t>#q-cross-04</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>https://www.global-png.com/act/pngFAQ.html#q-cross-02</t>
+          <t>https://www.global-png.com/act/pngFAQ.html#q-cross-04</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
@@ -1970,22 +1930,22 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>q-cross-03</t>
+          <t>q-cross-05</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>韩国二手设备市场的规模和特点？</t>
+          <t>跨境贸易额外成本估算（100 万美元二手 CVD 案例）</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>#q-cross-03</t>
+          <t>#q-cross-05</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t>https://www.global-png.com/act/pngFAQ.html#q-cross-03</t>
+          <t>https://www.global-png.com/act/pngFAQ.html#q-cross-05</t>
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr">
@@ -2003,22 +1963,22 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>q-cross-04</t>
+          <t>q-cross-06</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>韩国设备进口需要什么手续和资质？5 步完整流程</t>
+          <t>跨境贸易常见风险与对策</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>#q-cross-04</t>
+          <t>#q-cross-06</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>https://www.global-png.com/act/pngFAQ.html#q-cross-04</t>
+          <t>https://www.global-png.com/act/pngFAQ.html#q-cross-06</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
@@ -2036,22 +1996,22 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>q-cross-05</t>
+          <t>q-cross-07</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>跨境贸易额外成本估算（100 万美元二手 CVD 案例）</t>
+          <t>平台上的价格是最终价格吗？</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>#q-cross-05</t>
+          <t>#q-cross-07</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t>https://www.global-png.com/act/pngFAQ.html#q-cross-05</t>
+          <t>https://www.global-png.com/act/pngFAQ.html#q-cross-07</t>
         </is>
       </c>
       <c r="F36" s="5" t="inlineStr">
@@ -2069,22 +2029,22 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>q-cross-06</t>
+          <t>q-cross-08</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>跨境贸易常见风险与对策</t>
+          <t>哪些设备品类价格区间参考？</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>#q-cross-06</t>
+          <t>#q-cross-08</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t>https://www.global-png.com/act/pngFAQ.html#q-cross-06</t>
+          <t>https://www.global-png.com/act/pngFAQ.html#q-cross-08</t>
         </is>
       </c>
       <c r="F37" s="5" t="inlineStr">
@@ -2102,22 +2062,22 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>q-cross-07</t>
+          <t>q-cross-09</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>平台上的价格是最终价格吗？</t>
+          <t>二手设备能保修吗？</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>#q-cross-07</t>
+          <t>#q-cross-09</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
-          <t>https://www.global-png.com/act/pngFAQ.html#q-cross-07</t>
+          <t>https://www.global-png.com/act/pngFAQ.html#q-cross-09</t>
         </is>
       </c>
       <c r="F38" s="5" t="inlineStr">
@@ -2130,27 +2090,27 @@
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>跨境贸易（中韩双向专题）</t>
+          <t>供应商与代理商合作</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>q-cross-08</t>
+          <t>q-supplier-01</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>哪些设备品类价格区间参考？</t>
+          <t>供应商如何入驻平台？需要什么资质？</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>#q-cross-08</t>
+          <t>#q-supplier-01</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>https://www.global-png.com/act/pngFAQ.html#q-cross-08</t>
+          <t>https://www.global-png.com/act/pngFAQ.html#q-supplier-01</t>
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr">
@@ -2163,27 +2123,27 @@
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>跨境贸易（中韩双向专题）</t>
+          <t>供应商与代理商合作</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>q-cross-09</t>
+          <t>q-supplier-02</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>二手设备能保修吗？</t>
+          <t>供应商会员体系（基础/标准/战略）是什么？</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>#q-cross-09</t>
+          <t>#q-supplier-02</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
-          <t>https://www.global-png.com/act/pngFAQ.html#q-cross-09</t>
+          <t>https://www.global-png.com/act/pngFAQ.html#q-supplier-02</t>
         </is>
       </c>
       <c r="F40" s="5" t="inlineStr">
@@ -2201,22 +2161,22 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>q-supplier-01</t>
+          <t>q-supplier-03</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>供应商如何入驻平台？需要什么资质？</t>
+          <t>广告位规格与定价是什么？</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>#q-supplier-01</t>
+          <t>#q-supplier-03</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t>https://www.global-png.com/act/pngFAQ.html#q-supplier-01</t>
+          <t>https://www.global-png.com/act/pngFAQ.html#q-supplier-03</t>
         </is>
       </c>
       <c r="F41" s="5" t="inlineStr">
@@ -2234,22 +2194,22 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>q-supplier-02</t>
+          <t>q-supplier-04</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>供应商会员体系（基础/标准/战略）是什么？</t>
+          <t>代理商如何加盟？有什么优势？</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>#q-supplier-02</t>
+          <t>#q-supplier-04</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
-          <t>https://www.global-png.com/act/pngFAQ.html#q-supplier-02</t>
+          <t>https://www.global-png.com/act/pngFAQ.html#q-supplier-04</t>
         </is>
       </c>
       <c r="F42" s="5" t="inlineStr">
@@ -2260,41 +2220,37 @@
       <c r="G42" s="5" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="6" t="inlineStr">
+      <c r="A43" s="5" t="inlineStr">
         <is>
           <t>供应商与代理商合作</t>
         </is>
       </c>
-      <c r="B43" s="6" t="inlineStr">
-        <is>
-          <t>q-supplier-03</t>
-        </is>
-      </c>
-      <c r="C43" s="6" t="inlineStr">
-        <is>
-          <t>广告位规格与定价是什么？</t>
-        </is>
-      </c>
-      <c r="D43" s="6" t="inlineStr">
-        <is>
-          <t>#q-supplier-03</t>
-        </is>
-      </c>
-      <c r="E43" s="6" t="inlineStr">
-        <is>
-          <t>https://www.global-png.com/act/pngFAQ.html#q-supplier-03</t>
-        </is>
-      </c>
-      <c r="F43" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G43" s="6" t="inlineStr">
-        <is>
-          <t>表头部分列名缺失（空白列），需与原页面核对</t>
-        </is>
-      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>q-supplier-05</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>代理商 90 天陪跑计划是什么？具体怎么走？</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="inlineStr">
+        <is>
+          <t>#q-supplier-05</t>
+        </is>
+      </c>
+      <c r="E43" s="5" t="inlineStr">
+        <is>
+          <t>https://www.global-png.com/act/pngFAQ.html#q-supplier-05</t>
+        </is>
+      </c>
+      <c r="F43" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G43" s="5" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
@@ -2304,22 +2260,22 @@
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>q-supplier-04</t>
+          <t>q-supplier-06</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>代理商如何加盟？有什么优势？</t>
+          <t>代理商转化路径的三个核心是什么？</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>#q-supplier-04</t>
+          <t>#q-supplier-06</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
         <is>
-          <t>https://www.global-png.com/act/pngFAQ.html#q-supplier-04</t>
+          <t>https://www.global-png.com/act/pngFAQ.html#q-supplier-06</t>
         </is>
       </c>
       <c r="F44" s="5" t="inlineStr">
@@ -2337,22 +2293,22 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>q-supplier-05</t>
+          <t>q-supplier-07</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>代理商 90 天陪跑计划是什么？具体怎么走？</t>
+          <t>专家/学者如何加入平台？</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>#q-supplier-05</t>
+          <t>#q-supplier-07</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
         <is>
-          <t>https://www.global-png.com/act/pngFAQ.html#q-supplier-05</t>
+          <t>https://www.global-png.com/act/pngFAQ.html#q-supplier-07</t>
         </is>
       </c>
       <c r="F45" s="5" t="inlineStr">
@@ -2370,27 +2326,27 @@
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>q-supplier-06</t>
+          <t>q-supplier-08</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>代理商转化路径的三个核心是什么？</t>
+          <t>如何关注和管理供应商？</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>#q-supplier-06</t>
+          <t>#q-supplier-08</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
         <is>
-          <t>https://www.global-png.com/act/pngFAQ.html#q-supplier-06</t>
+          <t>https://www.global-png.com/act/pngFAQ.html#q-supplier-08</t>
         </is>
       </c>
       <c r="F46" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>followSupplier</t>
         </is>
       </c>
       <c r="G46" s="5" t="inlineStr"/>
@@ -2403,22 +2359,22 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>q-supplier-07</t>
+          <t>q-supplier-09</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>专家/学者如何加入平台？</t>
+          <t>认证企业专区是什么？</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>#q-supplier-07</t>
+          <t>#q-supplier-09</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
         <is>
-          <t>https://www.global-png.com/act/pngFAQ.html#q-supplier-07</t>
+          <t>https://www.global-png.com/act/pngFAQ.html#q-supplier-09</t>
         </is>
       </c>
       <c r="F47" s="5" t="inlineStr">
@@ -2431,32 +2387,32 @@
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>供应商与代理商合作</t>
+          <t>支付与财务</t>
         </is>
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>q-supplier-08</t>
+          <t>q-pay-01</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>如何关注和管理供应商？</t>
+          <t>平台支持哪些支付方式？</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>#q-supplier-08</t>
+          <t>#q-pay-01</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
         <is>
-          <t>https://www.global-png.com/act/pngFAQ.html#q-supplier-08</t>
+          <t>https://www.global-png.com/act/pngFAQ.html#q-pay-01</t>
         </is>
       </c>
       <c r="F48" s="5" t="inlineStr">
         <is>
-          <t>followSupplier</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G48" s="5" t="inlineStr"/>
@@ -2464,27 +2420,27 @@
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>供应商与代理商合作</t>
+          <t>支付与财务</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>q-supplier-09</t>
+          <t>q-pay-02</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>认证企业专区是什么？</t>
+          <t>信用账单系统如何运作？</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>#q-supplier-09</t>
+          <t>#q-pay-02</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
         <is>
-          <t>https://www.global-png.com/act/pngFAQ.html#q-supplier-09</t>
+          <t>https://www.global-png.com/act/pngFAQ.html#q-pay-02</t>
         </is>
       </c>
       <c r="F49" s="5" t="inlineStr">
@@ -2495,41 +2451,37 @@
       <c r="G49" s="5" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="6" t="inlineStr">
+      <c r="A50" s="5" t="inlineStr">
         <is>
           <t>支付与财务</t>
         </is>
       </c>
-      <c r="B50" s="6" t="inlineStr">
-        <is>
-          <t>q-pay-01</t>
-        </is>
-      </c>
-      <c r="C50" s="6" t="inlineStr">
-        <is>
-          <t>平台支持哪些支付方式？</t>
-        </is>
-      </c>
-      <c r="D50" s="6" t="inlineStr">
-        <is>
-          <t>#q-pay-01</t>
-        </is>
-      </c>
-      <c r="E50" s="6" t="inlineStr">
-        <is>
-          <t>https://www.global-png.com/act/pngFAQ.html#q-pay-01</t>
-        </is>
-      </c>
-      <c r="F50" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G50" s="6" t="inlineStr">
-        <is>
-          <t>“支付方式优先级推荐（跨境设备）”标题下的内容在保存时丢失，需补充</t>
-        </is>
-      </c>
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>q-pay-03</t>
+        </is>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>平台担保交易如何保护买卖双方？</t>
+        </is>
+      </c>
+      <c r="D50" s="5" t="inlineStr">
+        <is>
+          <t>#q-pay-03</t>
+        </is>
+      </c>
+      <c r="E50" s="5" t="inlineStr">
+        <is>
+          <t>https://www.global-png.com/act/pngFAQ.html#q-pay-03</t>
+        </is>
+      </c>
+      <c r="F50" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G50" s="5" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
@@ -2539,27 +2491,27 @@
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>q-pay-02</t>
+          <t>q-pay-04</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>信用账单系统如何运作？</t>
+          <t>如何管理发票和合同？</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>#q-pay-02</t>
+          <t>#q-pay-04</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
         <is>
-          <t>https://www.global-png.com/act/pngFAQ.html#q-pay-02</t>
+          <t>https://www.global-png.com/act/pngFAQ.html#q-pay-04</t>
         </is>
       </c>
       <c r="F51" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="G51" s="5" t="inlineStr"/>
@@ -2572,27 +2524,27 @@
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>q-pay-03</t>
+          <t>q-pay-05</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>平台担保交易如何保护买卖双方？</t>
+          <t>退货/退款如何处理？</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>#q-pay-03</t>
+          <t>#q-pay-05</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
         <is>
-          <t>https://www.global-png.com/act/pngFAQ.html#q-pay-03</t>
+          <t>https://www.global-png.com/act/pngFAQ.html#q-pay-05</t>
         </is>
       </c>
       <c r="F52" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>afterSalesReturn</t>
         </is>
       </c>
       <c r="G52" s="5" t="inlineStr"/>
@@ -2600,72 +2552,68 @@
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>支付与财务</t>
+          <t>行业知识与资源</t>
         </is>
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>q-pay-04</t>
+          <t>q-know-01</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>如何管理发票和合同？</t>
+          <t>平台提供哪些行业知识内容？</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>#q-pay-04</t>
+          <t>#q-know-01</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
         <is>
-          <t>https://www.global-png.com/act/pngFAQ.html#q-pay-04</t>
+          <t>https://www.global-png.com/act/pngFAQ.html#q-know-01</t>
         </is>
       </c>
       <c r="F53" s="5" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G53" s="5" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" s="6" t="inlineStr">
-        <is>
-          <t>支付与财务</t>
-        </is>
-      </c>
-      <c r="B54" s="6" t="inlineStr">
-        <is>
-          <t>q-pay-05</t>
-        </is>
-      </c>
-      <c r="C54" s="6" t="inlineStr">
-        <is>
-          <t>退货/退款如何处理？</t>
-        </is>
-      </c>
-      <c r="D54" s="6" t="inlineStr">
-        <is>
-          <t>#q-pay-05</t>
-        </is>
-      </c>
-      <c r="E54" s="6" t="inlineStr">
-        <is>
-          <t>https://www.global-png.com/act/pngFAQ.html#q-pay-05</t>
-        </is>
-      </c>
-      <c r="F54" s="6" t="inlineStr">
-        <is>
-          <t>afterSalesReturn</t>
-        </is>
-      </c>
-      <c r="G54" s="6" t="inlineStr">
-        <is>
-          <t>“特别说明（免运费专区）”标题下的内容在保存时丢失，需补充</t>
-        </is>
-      </c>
+      <c r="A54" s="5" t="inlineStr">
+        <is>
+          <t>行业知识与资源</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="inlineStr">
+        <is>
+          <t>q-know-02</t>
+        </is>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>泛半导体产业结构化综合报告包含什么？</t>
+        </is>
+      </c>
+      <c r="D54" s="5" t="inlineStr">
+        <is>
+          <t>#q-know-02</t>
+        </is>
+      </c>
+      <c r="E54" s="5" t="inlineStr">
+        <is>
+          <t>https://www.global-png.com/act/pngFAQ.html#q-know-02</t>
+        </is>
+      </c>
+      <c r="F54" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G54" s="5" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
@@ -2675,22 +2623,22 @@
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>q-know-01</t>
+          <t>q-know-03</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>平台提供哪些行业知识内容？</t>
+          <t>"资料下载"快捷入口是什么？</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>#q-know-01</t>
+          <t>#q-know-03</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
         <is>
-          <t>https://www.global-png.com/act/pngFAQ.html#q-know-01</t>
+          <t>https://www.global-png.com/act/pngFAQ.html#q-know-03</t>
         </is>
       </c>
       <c r="F55" s="5" t="inlineStr">
@@ -2708,22 +2656,22 @@
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>q-know-02</t>
+          <t>q-know-04</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>泛半导体产业结构化综合报告包含什么？</t>
+          <t>是否可以收藏文章和产品？</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>#q-know-02</t>
+          <t>#q-know-04</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr">
         <is>
-          <t>https://www.global-png.com/act/pngFAQ.html#q-know-02</t>
+          <t>https://www.global-png.com/act/pngFAQ.html#q-know-04</t>
         </is>
       </c>
       <c r="F56" s="5" t="inlineStr">
@@ -2741,22 +2689,22 @@
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>q-know-03</t>
+          <t>q-know-05</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>"资料下载"快捷入口是什么？</t>
+          <t>平台是否支持多语言？覆盖哪些站点？</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>#q-know-03</t>
+          <t>#q-know-05</t>
         </is>
       </c>
       <c r="E57" s="5" t="inlineStr">
         <is>
-          <t>https://www.global-png.com/act/pngFAQ.html#q-know-03</t>
+          <t>https://www.global-png.com/act/pngFAQ.html#q-know-05</t>
         </is>
       </c>
       <c r="F57" s="5" t="inlineStr">
@@ -2769,27 +2717,27 @@
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
         <is>
-          <t>行业知识与资源</t>
+          <t>新用户活动与增值服务</t>
         </is>
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>q-know-04</t>
+          <t>q-new-01</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>是否可以收藏文章和产品？</t>
+          <t>免运费专区规则是什么？新用户怎么享受？</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>#q-know-04</t>
+          <t>#q-new-01</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr">
         <is>
-          <t>https://www.global-png.com/act/pngFAQ.html#q-know-04</t>
+          <t>https://www.global-png.com/act/pngFAQ.html#q-new-01</t>
         </is>
       </c>
       <c r="F58" s="5" t="inlineStr">
@@ -2802,27 +2750,27 @@
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>行业知识与资源</t>
+          <t>新用户活动与增值服务</t>
         </is>
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>q-know-05</t>
+          <t>q-new-02</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>平台是否支持多语言？覆盖哪些站点？</t>
+          <t>平台还有哪些增值服务？</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>#q-know-05</t>
+          <t>#q-new-02</t>
         </is>
       </c>
       <c r="E59" s="5" t="inlineStr">
         <is>
-          <t>https://www.global-png.com/act/pngFAQ.html#q-know-05</t>
+          <t>https://www.global-png.com/act/pngFAQ.html#q-new-02</t>
         </is>
       </c>
       <c r="F59" s="5" t="inlineStr">
@@ -2832,74 +2780,8 @@
       </c>
       <c r="G59" s="5" t="inlineStr"/>
     </row>
-    <row r="60">
-      <c r="A60" s="5" t="inlineStr">
-        <is>
-          <t>新用户活动与增值服务</t>
-        </is>
-      </c>
-      <c r="B60" s="5" t="inlineStr">
-        <is>
-          <t>q-new-01</t>
-        </is>
-      </c>
-      <c r="C60" s="5" t="inlineStr">
-        <is>
-          <t>免运费专区规则是什么？新用户怎么享受？</t>
-        </is>
-      </c>
-      <c r="D60" s="5" t="inlineStr">
-        <is>
-          <t>#q-new-01</t>
-        </is>
-      </c>
-      <c r="E60" s="5" t="inlineStr">
-        <is>
-          <t>https://www.global-png.com/act/pngFAQ.html#q-new-01</t>
-        </is>
-      </c>
-      <c r="F60" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G60" s="5" t="inlineStr"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="5" t="inlineStr">
-        <is>
-          <t>新用户活动与增值服务</t>
-        </is>
-      </c>
-      <c r="B61" s="5" t="inlineStr">
-        <is>
-          <t>q-new-02</t>
-        </is>
-      </c>
-      <c r="C61" s="5" t="inlineStr">
-        <is>
-          <t>平台还有哪些增值服务？</t>
-        </is>
-      </c>
-      <c r="D61" s="5" t="inlineStr">
-        <is>
-          <t>#q-new-02</t>
-        </is>
-      </c>
-      <c r="E61" s="5" t="inlineStr">
-        <is>
-          <t>https://www.global-png.com/act/pngFAQ.html#q-new-02</t>
-        </is>
-      </c>
-      <c r="F61" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G61" s="5" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:G61"/>
+  <autoFilter ref="A1:G59"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2948,71 +2830,83 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="5" t="inlineStr">
         <is>
           <t>enterpriseAuth</t>
         </is>
       </c>
-      <c r="B2" s="6" t="inlineStr">
+      <c r="B2" s="5" t="inlineStr">
         <is>
           <t>用户中心 → 设置 → 企业认证</t>
         </is>
       </c>
-      <c r="C2" s="6" t="inlineStr"/>
-      <c r="D2" s="6" t="inlineStr">
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>https://www.global-png.com/member/authen</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
         <is>
           <t>q-account-02</t>
         </is>
       </c>
-      <c r="E2" s="6" t="inlineStr">
-        <is>
-          <t>待填写</t>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>已填写</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>materialCode</t>
         </is>
       </c>
-      <c r="B3" s="6" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>用户中心 → 采购管理 → 物料编码</t>
         </is>
       </c>
-      <c r="C3" s="6" t="inlineStr"/>
-      <c r="D3" s="6" t="inlineStr">
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>https://www.global-png.com/member/matCode</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
         <is>
           <t>q-product-07</t>
         </is>
       </c>
-      <c r="E3" s="6" t="inlineStr">
-        <is>
-          <t>待填写</t>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>已填写</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>subAccount</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>用户中心 → 企业管理 → 子账号管理</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr"/>
-      <c r="D4" s="6" t="inlineStr">
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>https://www.global-png.com/member/subAccount</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
         <is>
           <t>q-account-04</t>
         </is>
       </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>待填写</t>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>已填写</t>
         </is>
       </c>
     </row>
@@ -3027,7 +2921,11 @@
           <t>用户中心 → 设置 → 账户安全</t>
         </is>
       </c>
-      <c r="C5" s="6" t="inlineStr"/>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>https://www.global-png.com/member/account</t>
+        </is>
+      </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
           <t>q-account-03</t>
@@ -3035,30 +2933,34 @@
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>待填写</t>
+          <t>已填写（需登录确认页面）</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>addressManage</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>用户中心 → 设置 → 地址管理</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr"/>
-      <c r="D6" s="6" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>https://www.global-png.com/member/address/list</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>q-account-05</t>
         </is>
       </c>
-      <c r="E6" s="6" t="inlineStr">
-        <is>
-          <t>待填写</t>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>已填写</t>
         </is>
       </c>
     </row>
@@ -3073,7 +2975,11 @@
           <t>用户中心 → 关注中心 → 供应商</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr"/>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>https://www.global-png.com/member/collect</t>
+        </is>
+      </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
           <t>q-supplier-08</t>
@@ -3081,30 +2987,34 @@
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>待填写</t>
+          <t>已填写（需登录确认页面）</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>afterSalesReturn</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>用户中心 → 售后服务 → 退货</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr"/>
-      <c r="D8" s="6" t="inlineStr">
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>https://www.global-png.com/member/order/aftersales</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
         <is>
           <t>q-pay-05</t>
         </is>
       </c>
-      <c r="E8" s="6" t="inlineStr">
-        <is>
-          <t>待填写</t>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>已填写</t>
         </is>
       </c>
     </row>
@@ -3119,7 +3029,11 @@
           <t>用户中心 → 财务</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr"/>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>https://www.global-png.com/member/invoice</t>
+        </is>
+      </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
           <t>q-pay-04</t>
@@ -3127,30 +3041,34 @@
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>待填写</t>
+          <t>已填写（需登录确认页面）</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>myProject</t>
         </is>
       </c>
-      <c r="B10" s="6" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>我的项目</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr"/>
-      <c r="D10" s="6" t="inlineStr">
-        <is>
-          <t>预留（暂未使用）</t>
-        </is>
-      </c>
-      <c r="E10" s="6" t="inlineStr">
-        <is>
-          <t>待填写</t>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>https://www.global-png.com/member/project/list</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>q-order-06</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>已填写</t>
         </is>
       </c>
     </row>
@@ -3173,99 +3091,115 @@
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>待填写</t>
+          <t>待确认</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="inlineStr">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>frequentList</t>
         </is>
       </c>
-      <c r="B12" s="6" t="inlineStr">
+      <c r="B12" s="5" t="inlineStr">
         <is>
           <t>常购清单</t>
         </is>
       </c>
-      <c r="C12" s="6" t="inlineStr"/>
-      <c r="D12" s="6" t="inlineStr">
-        <is>
-          <t>预留（暂未使用）</t>
-        </is>
-      </c>
-      <c r="E12" s="6" t="inlineStr">
-        <is>
-          <t>待填写</t>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>https://www.global-png.com/member/regular/list</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>q-order-04</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>已填写</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="6" t="inlineStr">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t>myTender</t>
         </is>
       </c>
-      <c r="B13" s="6" t="inlineStr">
+      <c r="B13" s="5" t="inlineStr">
         <is>
           <t>我的招标</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr"/>
-      <c r="D13" s="6" t="inlineStr">
-        <is>
-          <t>预留（暂未使用）</t>
-        </is>
-      </c>
-      <c r="E13" s="6" t="inlineStr">
-        <is>
-          <t>待填写</t>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>https://www.global-png.com/member/bid</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>q-order-05</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>已填写</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="6" t="inlineStr">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>freeSample</t>
         </is>
       </c>
-      <c r="B14" s="6" t="inlineStr">
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t>免费申样</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr"/>
-      <c r="D14" s="6" t="inlineStr">
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>https://www.global-png.com/prototype/sample/apply</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
         <is>
           <t>页脚按钮「免费申样」</t>
         </is>
       </c>
-      <c r="E14" s="6" t="inlineStr">
-        <is>
-          <t>待填写</t>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>已填写</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="6" t="inlineStr">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>domesticAlt</t>
         </is>
       </c>
-      <c r="B15" s="6" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
         <is>
           <t>国产替代专区</t>
         </is>
       </c>
-      <c r="C15" s="6" t="inlineStr"/>
-      <c r="D15" s="6" t="inlineStr">
-        <is>
-          <t>页脚按钮「国产替代专区」</t>
-        </is>
-      </c>
-      <c r="E15" s="6" t="inlineStr">
-        <is>
-          <t>待填写</t>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>https://www.global-png.com/prototype/replacement/search</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>q-product-04</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>已填写</t>
         </is>
       </c>
     </row>
@@ -3285,8 +3219,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="56" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3307,15 +3241,19 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="5" t="inlineStr">
         <is>
           <t>在线客服</t>
         </is>
       </c>
-      <c r="B2" s="6" t="inlineStr"/>
-      <c r="C2" s="6" t="inlineStr">
-        <is>
-          <t>待确认（index.html 中 href 目前为 #）</t>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>https://www.global-png.com/service</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>已填写</t>
         </is>
       </c>
     </row>
@@ -3328,33 +3266,41 @@
       <c r="B3" s="6" t="inlineStr"/>
       <c r="C3" s="6" t="inlineStr">
         <is>
-          <t>待确认（index.html 中 href 目前为 #）</t>
+          <t>待确认（主站路由中未找到，href 目前为 #）</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>免费申样</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr"/>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>待确认（index.html 中 href 目前为 #）</t>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>https://www.global-png.com/prototype/sample/apply</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>已填写</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>国产替代专区</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr"/>
-      <c r="C5" s="6" t="inlineStr">
-        <is>
-          <t>待确认（index.html 中 href 目前为 #）</t>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>https://www.global-png.com/prototype/replacement/search</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>已填写</t>
         </is>
       </c>
     </row>
